--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_3.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0148887619757407</v>
+        <v>0.008225807597242915</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008407479917860684</v>
+        <v>0.008404691819872865</v>
       </c>
       <c r="C2" t="n">
-        <v>19089243</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>19089243</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>14025502</v>
+        <v>4652873</v>
       </c>
       <c r="L2" t="n">
-        <v>8263261</v>
+        <v>2725828</v>
       </c>
       <c r="M2" t="n">
-        <v>2122492</v>
+        <v>693387</v>
       </c>
       <c r="N2" t="n">
-        <v>124836</v>
+        <v>36301</v>
       </c>
       <c r="O2" t="n">
-        <v>1260640</v>
+        <v>416688</v>
       </c>
       <c r="P2" t="n">
-        <v>505371</v>
+        <v>167442</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999884963035583</v>
+        <v>0.9999921321868896</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9185037612915039</v>
+        <v>0.913499653339386</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8313528895378113</v>
+        <v>0.823790967464447</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7705135345458984</v>
+        <v>0.7700620889663696</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5681878924369812</v>
+        <v>0.5276461243629456</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8254983425140381</v>
+        <v>0.8224748969078064</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8755925297737122</v>
+        <v>0.8749510049819946</v>
       </c>
       <c r="X2" t="n">
-        <v>19089243</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>19089243</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>14599230</v>
+        <v>4849843</v>
       </c>
       <c r="AG2" t="n">
-        <v>8974181</v>
+        <v>2984316</v>
       </c>
       <c r="AH2" t="n">
-        <v>2405464</v>
+        <v>801097</v>
       </c>
       <c r="AI2" t="n">
-        <v>177545</v>
+        <v>59133</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1378044</v>
+        <v>459291</v>
       </c>
       <c r="AK2" t="n">
-        <v>540084</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566497802734375</v>
+        <v>0.9567072987556458</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112433791160583</v>
+        <v>0.9112796187400818</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580086231231689</v>
+        <v>0.8579719662666321</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622910499572754</v>
+        <v>0.6624432802200317</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.90196692943573</v>
+        <v>0.9019978642463684</v>
       </c>
       <c r="AR2" t="n">
         <v>0.9314266443252563</v>
@@ -786,425 +786,425 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.003546198011096648</v>
+        <v>0.001883812434438796</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002014200905435255</v>
+        <v>0.002014117820993523</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>14025502</v>
+        <v>4652873</v>
       </c>
       <c r="E3" t="n">
-        <v>1176459</v>
+        <v>403478</v>
       </c>
       <c r="F3" t="n">
-        <v>33045</v>
+        <v>7004</v>
       </c>
       <c r="G3" t="n">
-        <v>8834</v>
+        <v>806</v>
       </c>
       <c r="H3" t="n">
-        <v>1007</v>
+        <v>228</v>
       </c>
       <c r="I3" t="n">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>30288137</v>
+        <v>10069570</v>
       </c>
       <c r="K3" t="n">
-        <v>32888206</v>
+        <v>10911004</v>
       </c>
       <c r="L3" t="n">
-        <v>37839644</v>
+        <v>12553834</v>
       </c>
       <c r="M3" t="n">
-        <v>45940386</v>
+        <v>15274892</v>
       </c>
       <c r="N3" t="n">
-        <v>49014465</v>
+        <v>16294169</v>
       </c>
       <c r="O3" t="n">
-        <v>47582641</v>
+        <v>15816662</v>
       </c>
       <c r="P3" t="n">
-        <v>48725866</v>
+        <v>16198768</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9200096726417542</v>
+        <v>0.918739378452301</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8379159569740295</v>
+        <v>0.8312704563140869</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7566654682159424</v>
+        <v>0.7423326969146729</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4653510451316833</v>
+        <v>0.4063514471054077</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8247708678245544</v>
+        <v>0.8179992437362671</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8714359998703003</v>
+        <v>0.8662241697311401</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14599230</v>
+        <v>4849843</v>
       </c>
       <c r="Z3" t="n">
-        <v>599197</v>
+        <v>199096</v>
       </c>
       <c r="AA3" t="n">
-        <v>25799</v>
+        <v>8579</v>
       </c>
       <c r="AB3" t="n">
-        <v>20500</v>
+        <v>6817</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30288357</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>33471090</v>
+        <v>11132126</v>
       </c>
       <c r="AG3" t="n">
-        <v>38641818</v>
+        <v>12846342</v>
       </c>
       <c r="AH3" t="n">
-        <v>46174461</v>
+        <v>15349322</v>
       </c>
       <c r="AI3" t="n">
-        <v>49018806</v>
+        <v>16296534</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47699350</v>
+        <v>15856699</v>
       </c>
       <c r="AK3" t="n">
-        <v>48757909</v>
+        <v>16209445</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576436281204224</v>
+        <v>0.9576323628425598</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100050926208496</v>
+        <v>0.9100990891456604</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575446009635925</v>
+        <v>0.8576458692550659</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6618342995643616</v>
+        <v>0.6619316339492798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015821814537048</v>
+        <v>0.901633083820343</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312933087348938</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04496333663266985</v>
+        <v>0.02814058239170234</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03183515015025684</v>
+        <v>0.03182526122067923</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1178817</v>
+        <v>417462</v>
       </c>
       <c r="E4" t="n">
-        <v>8263261</v>
+        <v>2725828</v>
       </c>
       <c r="F4" t="n">
-        <v>385029</v>
+        <v>126610</v>
       </c>
       <c r="G4" t="n">
-        <v>13237</v>
+        <v>3111</v>
       </c>
       <c r="H4" t="n">
-        <v>19828</v>
+        <v>5726</v>
       </c>
       <c r="I4" t="n">
-        <v>1497</v>
+        <v>370</v>
       </c>
       <c r="J4" t="n">
-        <v>220</v>
+        <v>50</v>
       </c>
       <c r="K4" t="n">
-        <v>1244443</v>
+        <v>440586</v>
       </c>
       <c r="L4" t="n">
-        <v>1676274</v>
+        <v>583055</v>
       </c>
       <c r="M4" t="n">
-        <v>632154</v>
+        <v>207043</v>
       </c>
       <c r="N4" t="n">
-        <v>94873</v>
+        <v>32497</v>
       </c>
       <c r="O4" t="n">
-        <v>266486</v>
+        <v>89939</v>
       </c>
       <c r="P4" t="n">
-        <v>71805</v>
+        <v>23931</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999942183494568</v>
+        <v>0.9999960660934448</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9192560911178589</v>
+        <v>0.9161120057106018</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8346214890480042</v>
+        <v>0.8275138139724731</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7635267376899719</v>
+        <v>0.7559431791305542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5116533637046814</v>
+        <v>0.4591227471828461</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8251343965530396</v>
+        <v>0.820231020450592</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8735092878341675</v>
+        <v>0.8705657124519348</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>617717</v>
+        <v>204901</v>
       </c>
       <c r="Z4" t="n">
-        <v>8974181</v>
+        <v>2984316</v>
       </c>
       <c r="AA4" t="n">
-        <v>249583</v>
+        <v>83178</v>
       </c>
       <c r="AB4" t="n">
-        <v>16553</v>
+        <v>5500</v>
       </c>
       <c r="AC4" t="n">
-        <v>3444</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>661559</v>
+        <v>219464</v>
       </c>
       <c r="AG4" t="n">
-        <v>874100</v>
+        <v>290547</v>
       </c>
       <c r="AH4" t="n">
-        <v>398079</v>
+        <v>132613</v>
       </c>
       <c r="AI4" t="n">
-        <v>90532</v>
+        <v>30132</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149777</v>
+        <v>49902</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571464657783508</v>
+        <v>0.9571695923805237</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106237292289734</v>
+        <v>0.9106889963150024</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8577765226364136</v>
+        <v>0.8578088283538818</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6620625853538513</v>
+        <v>0.6621873378753662</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.901774525642395</v>
+        <v>0.9018154144287109</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313599467277527</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>38897</v>
+        <v>13751</v>
       </c>
       <c r="E5" t="n">
-        <v>446930</v>
+        <v>159188</v>
       </c>
       <c r="F5" t="n">
-        <v>2122492</v>
+        <v>693387</v>
       </c>
       <c r="G5" t="n">
-        <v>39178</v>
+        <v>14732</v>
       </c>
       <c r="H5" t="n">
-        <v>149309</v>
+        <v>50622</v>
       </c>
       <c r="I5" t="n">
-        <v>8249</v>
+        <v>2385</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1219449</v>
+        <v>411537</v>
       </c>
       <c r="L5" t="n">
-        <v>1598421</v>
+        <v>553283</v>
       </c>
       <c r="M5" t="n">
-        <v>682568</v>
+        <v>240678</v>
       </c>
       <c r="N5" t="n">
-        <v>143426</v>
+        <v>53033</v>
       </c>
       <c r="O5" t="n">
-        <v>267833</v>
+        <v>92711</v>
       </c>
       <c r="P5" t="n">
-        <v>74558</v>
+        <v>25859</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999955296516418</v>
+        <v>0.9999969601631165</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9501010179519653</v>
+        <v>0.9480919241905212</v>
       </c>
       <c r="S5" t="n">
-        <v>0.933680534362793</v>
+        <v>0.9307786226272583</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9733741283416748</v>
+        <v>0.9727265238761902</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9951739311218262</v>
+        <v>0.9947898387908936</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9891788959503174</v>
+        <v>0.9888736605644226</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9970358610153198</v>
+        <v>0.9969669580459595</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>24202</v>
+        <v>8036</v>
       </c>
       <c r="Z5" t="n">
-        <v>256091</v>
+        <v>85188</v>
       </c>
       <c r="AA5" t="n">
-        <v>2405464</v>
+        <v>801097</v>
       </c>
       <c r="AB5" t="n">
-        <v>29911</v>
+        <v>9959</v>
       </c>
       <c r="AC5" t="n">
-        <v>87493</v>
+        <v>29152</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>645721</v>
+        <v>214567</v>
       </c>
       <c r="AG5" t="n">
-        <v>887501</v>
+        <v>294795</v>
       </c>
       <c r="AH5" t="n">
-        <v>399596</v>
+        <v>132968</v>
       </c>
       <c r="AI5" t="n">
-        <v>90717</v>
+        <v>30201</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150429</v>
+        <v>50108</v>
       </c>
       <c r="AK5" t="n">
-        <v>39845</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973524808883667</v>
+        <v>0.9735605120658875</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964323878288269</v>
+        <v>0.9643431901931763</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838454127311707</v>
+        <v>0.9838218092918396</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963293075561523</v>
+        <v>0.9963247179985046</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939202070236206</v>
+        <v>0.9939077496528625</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983878135681152</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>26596</v>
+        <v>9327</v>
       </c>
       <c r="E6" t="n">
-        <v>33221</v>
+        <v>14903</v>
       </c>
       <c r="F6" t="n">
-        <v>52611</v>
+        <v>18521</v>
       </c>
       <c r="G6" t="n">
-        <v>124836</v>
+        <v>36301</v>
       </c>
       <c r="H6" t="n">
-        <v>28443</v>
+        <v>9505</v>
       </c>
       <c r="I6" t="n">
-        <v>2525</v>
+        <v>766</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19472</v>
+        <v>6471</v>
       </c>
       <c r="Z6" t="n">
-        <v>16132</v>
+        <v>5370</v>
       </c>
       <c r="AA6" t="n">
-        <v>32697</v>
+        <v>10891</v>
       </c>
       <c r="AB6" t="n">
-        <v>177545</v>
+        <v>59133</v>
       </c>
       <c r="AC6" t="n">
-        <v>20973</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>18717</v>
+        <v>5239</v>
       </c>
       <c r="F7" t="n">
-        <v>157446</v>
+        <v>53705</v>
       </c>
       <c r="G7" t="n">
-        <v>32100</v>
+        <v>13340</v>
       </c>
       <c r="H7" t="n">
-        <v>1260640</v>
+        <v>416688</v>
       </c>
       <c r="I7" t="n">
-        <v>59433</v>
+        <v>20389</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2437</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>89010</v>
+        <v>29635</v>
       </c>
       <c r="AB7" t="n">
-        <v>22772</v>
+        <v>7591</v>
       </c>
       <c r="AC7" t="n">
-        <v>1378044</v>
+        <v>459291</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="E8" t="n">
-        <v>947</v>
+        <v>247</v>
       </c>
       <c r="F8" t="n">
-        <v>4023</v>
+        <v>1203</v>
       </c>
       <c r="G8" t="n">
-        <v>1524</v>
+        <v>508</v>
       </c>
       <c r="H8" t="n">
-        <v>67899</v>
+        <v>23858</v>
       </c>
       <c r="I8" t="n">
-        <v>505371</v>
+        <v>167442</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>796</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37732</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540084</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
